--- a/artfynd/A 9770-2024 artfynd.xlsx
+++ b/artfynd/A 9770-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114533522</v>
+        <v>114532939</v>
       </c>
       <c r="B2" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,12 +709,12 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588174</v>
+        <v>588329</v>
       </c>
       <c r="R2" t="n">
-        <v>6425374</v>
+        <v>6425463</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,6 +758,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-02-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Lyfte från marken.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,37 +789,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114532939</v>
+        <v>114533522</v>
       </c>
       <c r="B3" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,12 +823,12 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588329</v>
+        <v>588174</v>
       </c>
       <c r="R3" t="n">
-        <v>6425463</v>
+        <v>6425374</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,11 +872,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-02-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lyfte från marken.</t>
         </is>
       </c>
       <c r="AD3" t="b">
